--- a/Reports/score_summary.xlsx
+++ b/Reports/score_summary.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.54000000000001</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.34999999999999</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.48</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>341.43</v>
+        <v>298.08</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67.20999999999999</v>
+        <v>69.41</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88.31</v>
+        <v>89.31</v>
       </c>
     </row>
   </sheetData>
